--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107076</v>
+        <v>121107075</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,43 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455342</v>
+        <v>455341</v>
       </c>
       <c r="R5" t="n">
-        <v>7037319</v>
+        <v>7037311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1130,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107072</v>
+        <v>121107073</v>
       </c>
       <c r="B6" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1164,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455342</v>
+        <v>455347</v>
       </c>
       <c r="R6" t="n">
-        <v>7037294</v>
+        <v>7037308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107075</v>
+        <v>121107074</v>
       </c>
       <c r="B7" t="n">
-        <v>77535</v>
+        <v>74708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107081</v>
+        <v>121107085</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>79137</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,38 +1433,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1352</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455314</v>
+        <v>455213</v>
       </c>
       <c r="R8" t="n">
-        <v>7037357</v>
+        <v>7037273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,7 +1505,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,12 +1529,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I lövskog, med sälg, gråal</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107077</v>
+        <v>121107081</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>79717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,20 +1574,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1583,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455339</v>
+        <v>455314</v>
       </c>
       <c r="R9" t="n">
-        <v>7037327</v>
+        <v>7037357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1647,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,22 +1661,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,10 +1684,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107082</v>
+        <v>121107072</v>
       </c>
       <c r="B10" t="n">
-        <v>79680</v>
+        <v>74708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,43 +1700,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455314</v>
+        <v>455342</v>
       </c>
       <c r="R10" t="n">
-        <v>7037356</v>
+        <v>7037294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,12 +1783,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1806,10 +1816,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107079</v>
+        <v>121107086</v>
       </c>
       <c r="B11" t="n">
-        <v>100337</v>
+        <v>79137</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,38 +1828,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1352</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455347</v>
+        <v>455210</v>
       </c>
       <c r="R11" t="n">
-        <v>7037326</v>
+        <v>7037259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,7 +1900,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1891,7 +1910,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,7 +1924,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1923,10 +1957,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107087</v>
+        <v>121107077</v>
       </c>
       <c r="B12" t="n">
-        <v>79134</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1939,43 +1973,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455203</v>
+        <v>455339</v>
       </c>
       <c r="R12" t="n">
-        <v>7037250</v>
+        <v>7037327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2007,7 +2032,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2017,7 +2042,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,22 +2056,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2064,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107085</v>
+        <v>121107087</v>
       </c>
       <c r="B13" t="n">
-        <v>79134</v>
+        <v>79137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2099,7 +2124,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2113,10 +2138,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455213</v>
+        <v>455203</v>
       </c>
       <c r="R13" t="n">
-        <v>7037273</v>
+        <v>7037250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2148,7 +2173,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2158,7 +2183,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,7 +2197,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>I lövskog, med sälg, gråal</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2205,10 +2230,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107086</v>
+        <v>121107079</v>
       </c>
       <c r="B14" t="n">
-        <v>79134</v>
+        <v>100347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,47 +2242,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455210</v>
+        <v>455347</v>
       </c>
       <c r="R14" t="n">
-        <v>7037259</v>
+        <v>7037326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2305,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2299,7 +2315,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,22 +2329,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2346,10 +2347,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107074</v>
+        <v>121107082</v>
       </c>
       <c r="B15" t="n">
-        <v>74705</v>
+        <v>79683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2362,34 +2363,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455341</v>
+        <v>455314</v>
       </c>
       <c r="R15" t="n">
-        <v>7037311</v>
+        <v>7037356</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2421,7 +2431,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2431,7 +2441,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,22 +2455,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107073</v>
+        <v>121107083</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>79586</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2490,47 +2490,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455347</v>
+        <v>455313</v>
       </c>
       <c r="R16" t="n">
-        <v>7037308</v>
+        <v>7037356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2553,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2572,7 +2563,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2586,22 +2577,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2619,10 +2610,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107083</v>
+        <v>121107076</v>
       </c>
       <c r="B17" t="n">
-        <v>79583</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2631,38 +2622,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455313</v>
+        <v>455342</v>
       </c>
       <c r="R17" t="n">
-        <v>7037356</v>
+        <v>7037319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120752457</v>
+        <v>120752474</v>
       </c>
       <c r="B18" t="n">
-        <v>79583</v>
+        <v>79137</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2763,41 +2763,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>MD9:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD0:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455316</v>
+        <v>455189</v>
       </c>
       <c r="R18" t="n">
-        <v>7037365</v>
+        <v>7037247</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,10 +2863,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120752474</v>
+        <v>120752457</v>
       </c>
       <c r="B19" t="n">
-        <v>79134</v>
+        <v>79586</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2875,41 +2875,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MD0:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD9:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455189</v>
+        <v>455316</v>
       </c>
       <c r="R19" t="n">
-        <v>7037247</v>
+        <v>7037365</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107087</v>
+        <v>121107079</v>
       </c>
       <c r="B13" t="n">
-        <v>79137</v>
+        <v>100347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,47 +2101,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455203</v>
+        <v>455347</v>
       </c>
       <c r="R13" t="n">
-        <v>7037250</v>
+        <v>7037326</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2173,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2183,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,22 +2188,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2230,10 +2206,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107079</v>
+        <v>121107087</v>
       </c>
       <c r="B14" t="n">
-        <v>100347</v>
+        <v>79137</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2242,38 +2218,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1352</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455347</v>
+        <v>455203</v>
       </c>
       <c r="R14" t="n">
-        <v>7037326</v>
+        <v>7037250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,7 +2290,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2315,7 +2300,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,7 +2314,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107079</v>
+        <v>121107087</v>
       </c>
       <c r="B13" t="n">
-        <v>100347</v>
+        <v>79137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,38 +2101,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1352</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455347</v>
+        <v>455203</v>
       </c>
       <c r="R13" t="n">
-        <v>7037326</v>
+        <v>7037250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2164,7 +2173,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,7 +2183,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2188,7 +2197,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2206,10 +2230,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107087</v>
+        <v>121107079</v>
       </c>
       <c r="B14" t="n">
-        <v>79137</v>
+        <v>100347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2218,47 +2242,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455203</v>
+        <v>455347</v>
       </c>
       <c r="R14" t="n">
-        <v>7037250</v>
+        <v>7037326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2290,7 +2305,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2300,7 +2315,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,22 +2329,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107075</v>
+        <v>121107085</v>
       </c>
       <c r="B5" t="n">
-        <v>77538</v>
+        <v>79137</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>1352</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455341</v>
+        <v>455213</v>
       </c>
       <c r="R5" t="n">
-        <v>7037311</v>
+        <v>7037273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1124,22 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I lövskog, med sälg, gråal</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107073</v>
+        <v>121107076</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1183,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1197,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455347</v>
+        <v>455342</v>
       </c>
       <c r="R6" t="n">
-        <v>7037308</v>
+        <v>7037319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1280,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1289,7 +1298,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107074</v>
+        <v>121107072</v>
       </c>
       <c r="B7" t="n">
         <v>74708</v>
@@ -1329,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455341</v>
+        <v>455342</v>
       </c>
       <c r="R7" t="n">
-        <v>7037311</v>
+        <v>7037294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1373,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1383,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1412,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1421,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107085</v>
+        <v>121107075</v>
       </c>
       <c r="B8" t="n">
-        <v>79137</v>
+        <v>77538</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,43 +1446,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1352</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455213</v>
+        <v>455341</v>
       </c>
       <c r="R8" t="n">
-        <v>7037273</v>
+        <v>7037311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>I lövskog, med sälg, gråal</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107081</v>
+        <v>121107073</v>
       </c>
       <c r="B9" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,20 +1574,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1595,17 +1595,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455314</v>
+        <v>455347</v>
       </c>
       <c r="R9" t="n">
-        <v>7037357</v>
+        <v>7037308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,7 +1646,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1647,7 +1656,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,12 +1670,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1684,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107072</v>
+        <v>121107079</v>
       </c>
       <c r="B10" t="n">
-        <v>74708</v>
+        <v>100347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1696,25 +1715,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1724,10 +1743,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455342</v>
+        <v>455347</v>
       </c>
       <c r="R10" t="n">
-        <v>7037294</v>
+        <v>7037326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,7 +1778,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1788,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,22 +1802,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107086</v>
+        <v>121107077</v>
       </c>
       <c r="B11" t="n">
-        <v>79137</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1832,43 +1836,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455210</v>
+        <v>455339</v>
       </c>
       <c r="R11" t="n">
-        <v>7037259</v>
+        <v>7037327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1910,7 +1905,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,22 +1919,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1957,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107077</v>
+        <v>121107083</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>79586</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1969,25 +1964,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1997,10 +1992,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455339</v>
+        <v>455313</v>
       </c>
       <c r="R12" t="n">
-        <v>7037327</v>
+        <v>7037356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,7 +2027,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2042,7 +2037,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,22 +2051,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107079</v>
+        <v>121107074</v>
       </c>
       <c r="B14" t="n">
-        <v>100347</v>
+        <v>74708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2242,25 +2237,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455347</v>
+        <v>455341</v>
       </c>
       <c r="R14" t="n">
-        <v>7037326</v>
+        <v>7037311</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,7 +2300,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2315,7 +2310,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,7 +2324,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2347,10 +2357,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107082</v>
+        <v>121107086</v>
       </c>
       <c r="B15" t="n">
-        <v>79683</v>
+        <v>79137</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2363,26 +2373,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1352</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2392,14 +2402,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455314</v>
+        <v>455210</v>
       </c>
       <c r="R15" t="n">
-        <v>7037356</v>
+        <v>7037259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2431,7 +2441,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2441,7 +2451,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2455,12 +2465,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2478,10 +2498,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107083</v>
+        <v>121107082</v>
       </c>
       <c r="B16" t="n">
-        <v>79586</v>
+        <v>79683</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2490,35 +2510,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455313</v>
+        <v>455314</v>
       </c>
       <c r="R16" t="n">
         <v>7037356</v>
@@ -2553,7 +2582,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2563,7 +2592,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2580,19 +2609,9 @@
           <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2610,10 +2629,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107076</v>
+        <v>121107081</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2622,20 +2641,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2643,26 +2662,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455342</v>
+        <v>455314</v>
       </c>
       <c r="R17" t="n">
-        <v>7037319</v>
+        <v>7037357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2704,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,7 +2714,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2718,22 +2728,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107085</v>
+        <v>121107079</v>
       </c>
       <c r="B5" t="n">
-        <v>79137</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,47 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455213</v>
+        <v>455347</v>
       </c>
       <c r="R5" t="n">
-        <v>7037273</v>
+        <v>7037326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1115,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>I lövskog, med sälg, gråal</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107076</v>
+        <v>121107075</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,43 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455342</v>
+        <v>455341</v>
       </c>
       <c r="R6" t="n">
-        <v>7037319</v>
+        <v>7037311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1247,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1298,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107072</v>
+        <v>121107073</v>
       </c>
       <c r="B7" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,34 +1281,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455342</v>
+        <v>455347</v>
       </c>
       <c r="R7" t="n">
-        <v>7037294</v>
+        <v>7037308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1383,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,7 +1388,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1430,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107075</v>
+        <v>121107074</v>
       </c>
       <c r="B8" t="n">
-        <v>77538</v>
+        <v>74710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,21 +1422,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1505,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1520,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107073</v>
+        <v>121107072</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>74710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,43 +1554,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455347</v>
+        <v>455342</v>
       </c>
       <c r="R9" t="n">
-        <v>7037308</v>
+        <v>7037294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,7 +1613,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1656,7 +1623,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,7 +1652,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1703,10 +1670,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107079</v>
+        <v>121107082</v>
       </c>
       <c r="B10" t="n">
-        <v>100347</v>
+        <v>79686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1715,38 +1682,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455347</v>
+        <v>455314</v>
       </c>
       <c r="R10" t="n">
-        <v>7037326</v>
+        <v>7037356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1778,7 +1754,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1788,7 +1764,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1802,7 +1778,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1823,7 +1804,7 @@
         <v>121107077</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1952,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107083</v>
+        <v>121107086</v>
       </c>
       <c r="B12" t="n">
-        <v>79586</v>
+        <v>79140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1964,38 +1945,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455313</v>
+        <v>455210</v>
       </c>
       <c r="R12" t="n">
-        <v>7037356</v>
+        <v>7037259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2027,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2037,7 +2027,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,22 +2041,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2084,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107087</v>
+        <v>121107085</v>
       </c>
       <c r="B13" t="n">
-        <v>79137</v>
+        <v>79140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2119,7 +2109,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,10 +2123,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455203</v>
+        <v>455213</v>
       </c>
       <c r="R13" t="n">
-        <v>7037250</v>
+        <v>7037273</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,7 +2158,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2178,7 +2168,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,7 +2182,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>I lövskog, med sälg, gråal</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2225,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107074</v>
+        <v>121107076</v>
       </c>
       <c r="B14" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2241,34 +2231,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455341</v>
+        <v>455342</v>
       </c>
       <c r="R14" t="n">
-        <v>7037311</v>
+        <v>7037319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2300,7 +2299,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2310,7 +2309,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2339,7 +2338,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2357,10 +2356,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107086</v>
+        <v>121107083</v>
       </c>
       <c r="B15" t="n">
-        <v>79137</v>
+        <v>79589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2369,47 +2368,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455210</v>
+        <v>455313</v>
       </c>
       <c r="R15" t="n">
-        <v>7037259</v>
+        <v>7037356</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2441,7 +2431,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2451,7 +2441,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2465,22 +2455,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2498,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107082</v>
+        <v>121107081</v>
       </c>
       <c r="B16" t="n">
-        <v>79683</v>
+        <v>79720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2510,37 +2500,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
@@ -2550,7 +2531,7 @@
         <v>455314</v>
       </c>
       <c r="R16" t="n">
-        <v>7037356</v>
+        <v>7037357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2582,7 +2563,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2592,7 +2573,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2629,10 +2610,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107081</v>
+        <v>121107087</v>
       </c>
       <c r="B17" t="n">
-        <v>79717</v>
+        <v>79140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2641,38 +2622,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>1352</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455314</v>
+        <v>455203</v>
       </c>
       <c r="R17" t="n">
-        <v>7037357</v>
+        <v>7037250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2704,7 +2694,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2714,7 +2704,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,12 +2718,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
         <v>120752474</v>
       </c>
       <c r="B18" t="n">
-        <v>79137</v>
+        <v>79140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>120752457</v>
       </c>
       <c r="B19" t="n">
-        <v>79586</v>
+        <v>79589</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107079</v>
+        <v>121107077</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455347</v>
+        <v>455339</v>
       </c>
       <c r="R5" t="n">
-        <v>7037326</v>
+        <v>7037327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,6 +1116,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>I västbrant med asprik granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1126,17 +1141,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107075</v>
+        <v>121107082</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
+        <v>79686</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1164,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455341</v>
+        <v>455314</v>
       </c>
       <c r="R6" t="n">
-        <v>7037311</v>
+        <v>7037356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1256,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1258,17 +1272,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107073</v>
+        <v>121107081</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>79720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,20 +1291,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1298,26 +1312,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455347</v>
+        <v>455314</v>
       </c>
       <c r="R7" t="n">
-        <v>7037308</v>
+        <v>7037357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1378,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1399,17 +1394,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107074</v>
+        <v>121107073</v>
       </c>
       <c r="B8" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,34 +1417,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455341</v>
+        <v>455347</v>
       </c>
       <c r="R8" t="n">
-        <v>7037311</v>
+        <v>7037308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1524,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1531,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107072</v>
+        <v>121107083</v>
       </c>
       <c r="B9" t="n">
-        <v>74710</v>
+        <v>79589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455342</v>
+        <v>455313</v>
       </c>
       <c r="R9" t="n">
-        <v>7037294</v>
+        <v>7037356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,22 +1641,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,17 +1667,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107082</v>
+        <v>121107072</v>
       </c>
       <c r="B10" t="n">
-        <v>79686</v>
+        <v>74710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,43 +1690,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455314</v>
+        <v>455342</v>
       </c>
       <c r="R10" t="n">
-        <v>7037356</v>
+        <v>7037294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,7 +1749,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1764,7 +1759,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,12 +1773,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1794,14 +1799,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107077</v>
+        <v>121107076</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1834,17 +1839,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455339</v>
+        <v>455342</v>
       </c>
       <c r="R11" t="n">
-        <v>7037327</v>
+        <v>7037319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1890,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1886,7 +1900,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,7 +1914,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1926,17 +1940,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107086</v>
+        <v>121107079</v>
       </c>
       <c r="B12" t="n">
-        <v>79140</v>
+        <v>100361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1945,47 +1959,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455210</v>
+        <v>455347</v>
       </c>
       <c r="R12" t="n">
-        <v>7037259</v>
+        <v>7037326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,7 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,22 +2046,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2067,7 +2057,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2208,17 +2198,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107076</v>
+        <v>121107087</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>79140</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2231,26 +2221,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2260,14 +2250,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455342</v>
+        <v>455203</v>
       </c>
       <c r="R14" t="n">
-        <v>7037319</v>
+        <v>7037250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2299,7 +2289,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2309,7 +2299,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2323,22 +2313,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,17 +2339,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107083</v>
+        <v>121107074</v>
       </c>
       <c r="B15" t="n">
-        <v>79589</v>
+        <v>74710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2368,25 +2358,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2396,10 +2386,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455313</v>
+        <v>455341</v>
       </c>
       <c r="R15" t="n">
-        <v>7037356</v>
+        <v>7037311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2431,7 +2421,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2441,7 +2431,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2455,22 +2445,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2481,17 +2471,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107081</v>
+        <v>121107075</v>
       </c>
       <c r="B16" t="n">
-        <v>79720</v>
+        <v>77541</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2500,25 +2490,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2528,10 +2518,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455314</v>
+        <v>455341</v>
       </c>
       <c r="R16" t="n">
-        <v>7037357</v>
+        <v>7037311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2563,7 +2553,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2573,7 +2563,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2587,12 +2577,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107087</v>
+        <v>121107086</v>
       </c>
       <c r="B17" t="n">
         <v>79140</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455203</v>
+        <v>455210</v>
       </c>
       <c r="R17" t="n">
-        <v>7037250</v>
+        <v>7037259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107077</v>
+        <v>121107073</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,17 +1049,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455339</v>
+        <v>455347</v>
       </c>
       <c r="R5" t="n">
-        <v>7037327</v>
+        <v>7037308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1124,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1130,7 +1139,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1141,17 +1150,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107082</v>
+        <v>121107072</v>
       </c>
       <c r="B6" t="n">
-        <v>79686</v>
+        <v>74713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,43 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455314</v>
+        <v>455342</v>
       </c>
       <c r="R6" t="n">
-        <v>7037356</v>
+        <v>7037294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,12 +1256,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1272,17 +1282,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107081</v>
+        <v>121107076</v>
       </c>
       <c r="B7" t="n">
-        <v>79720</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,20 +1301,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1312,17 +1322,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455314</v>
+        <v>455342</v>
       </c>
       <c r="R7" t="n">
-        <v>7037357</v>
+        <v>7037319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1373,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1383,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,12 +1397,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1394,17 +1423,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107073</v>
+        <v>121107083</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>79592</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,47 +1442,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455347</v>
+        <v>455313</v>
       </c>
       <c r="R8" t="n">
-        <v>7037308</v>
+        <v>7037356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1505,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,22 +1529,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1535,17 +1555,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107083</v>
+        <v>121107081</v>
       </c>
       <c r="B9" t="n">
-        <v>79589</v>
+        <v>79723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,21 +1578,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1582,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455313</v>
+        <v>455314</v>
       </c>
       <c r="R9" t="n">
-        <v>7037356</v>
+        <v>7037357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,7 +1647,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,19 +1664,9 @@
           <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1667,17 +1677,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107072</v>
+        <v>121107075</v>
       </c>
       <c r="B10" t="n">
-        <v>74710</v>
+        <v>77544</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,21 +1700,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1714,10 +1724,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455342</v>
+        <v>455341</v>
       </c>
       <c r="R10" t="n">
-        <v>7037294</v>
+        <v>7037311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1759,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,7 +1798,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1799,17 +1809,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107076</v>
+        <v>121107077</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1839,26 +1849,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455342</v>
+        <v>455339</v>
       </c>
       <c r="R11" t="n">
-        <v>7037319</v>
+        <v>7037327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1890,7 +1891,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1900,7 +1901,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1915,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1940,17 +1941,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107079</v>
+        <v>121107087</v>
       </c>
       <c r="B12" t="n">
-        <v>100361</v>
+        <v>79143</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1959,38 +1960,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455347</v>
+        <v>455203</v>
       </c>
       <c r="R12" t="n">
-        <v>7037326</v>
+        <v>7037250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2022,7 +2032,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2042,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,7 +2056,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,7 +2082,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2067,7 +2092,7 @@
         <v>121107085</v>
       </c>
       <c r="B13" t="n">
-        <v>79140</v>
+        <v>79143</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2198,17 +2223,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107087</v>
+        <v>121107079</v>
       </c>
       <c r="B14" t="n">
-        <v>79140</v>
+        <v>100364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,47 +2242,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1352</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455203</v>
+        <v>455347</v>
       </c>
       <c r="R14" t="n">
-        <v>7037250</v>
+        <v>7037326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2305,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2299,7 +2315,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,22 +2329,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På sälg # Salix caprea</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2339,7 +2340,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2349,7 +2350,7 @@
         <v>121107074</v>
       </c>
       <c r="B15" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2471,17 +2472,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107075</v>
+        <v>121107086</v>
       </c>
       <c r="B16" t="n">
-        <v>77541</v>
+        <v>79143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2494,34 +2495,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1352</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455341</v>
+        <v>455210</v>
       </c>
       <c r="R16" t="n">
-        <v>7037311</v>
+        <v>7037259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2553,7 +2563,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2563,7 +2573,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2577,22 +2587,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2603,17 +2613,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107086</v>
+        <v>121107082</v>
       </c>
       <c r="B17" t="n">
-        <v>79140</v>
+        <v>79689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2626,26 +2636,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1352</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2655,14 +2665,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455210</v>
+        <v>455314</v>
       </c>
       <c r="R17" t="n">
-        <v>7037259</v>
+        <v>7037356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2704,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,7 +2714,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2718,22 +2728,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
         <v>120752474</v>
       </c>
       <c r="B18" t="n">
-        <v>79140</v>
+        <v>79143</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>120752457</v>
       </c>
       <c r="B19" t="n">
-        <v>79589</v>
+        <v>79592</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 27492-2024 artfynd.xlsx
+++ b/artfynd/A 27492-2024 artfynd.xlsx
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121107073</v>
+        <v>121107076</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455347</v>
+        <v>455342</v>
       </c>
       <c r="R5" t="n">
-        <v>7037308</v>
+        <v>7037319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På gran # Picea abies</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107072</v>
+        <v>121107082</v>
       </c>
       <c r="B6" t="n">
-        <v>74713</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1173,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455342</v>
+        <v>455314</v>
       </c>
       <c r="R6" t="n">
-        <v>7037294</v>
+        <v>7037356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,22 +1265,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1289,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107076</v>
+        <v>121107079</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,47 +1300,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455342</v>
+        <v>455347</v>
       </c>
       <c r="R7" t="n">
-        <v>7037319</v>
+        <v>7037326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1383,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,22 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1430,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107083</v>
+        <v>121107075</v>
       </c>
       <c r="B8" t="n">
-        <v>79592</v>
+        <v>77544</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,25 +1417,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1470,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455313</v>
+        <v>455341</v>
       </c>
       <c r="R8" t="n">
-        <v>7037356</v>
+        <v>7037311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,22 +1504,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp # Populus tremula</t>
+          <t>Rikligt på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1537,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107081</v>
+        <v>121107085</v>
       </c>
       <c r="B9" t="n">
-        <v>79723</v>
+        <v>79143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,38 +1549,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1352</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455314</v>
+        <v>455213</v>
       </c>
       <c r="R9" t="n">
-        <v>7037357</v>
+        <v>7037273</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,7 +1621,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1647,7 +1631,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,12 +1645,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I lövskog, med sälg, gråal</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1684,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107075</v>
+        <v>121107073</v>
       </c>
       <c r="B10" t="n">
-        <v>77544</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1700,34 +1694,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455341</v>
+        <v>455347</v>
       </c>
       <c r="R10" t="n">
-        <v>7037311</v>
+        <v>7037308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,7 +1762,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1772,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,7 +1801,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran # Picea abies</t>
+          <t>På gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,10 +1819,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107077</v>
+        <v>121107081</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>79723</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,20 +1831,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1856,10 +1859,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455339</v>
+        <v>455314</v>
       </c>
       <c r="R11" t="n">
-        <v>7037327</v>
+        <v>7037357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,7 +1894,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1901,7 +1904,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,22 +1918,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På äldre gran # Picea abies</t>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1948,10 +1941,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107087</v>
+        <v>121107074</v>
       </c>
       <c r="B12" t="n">
-        <v>79143</v>
+        <v>74713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1964,43 +1957,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1352</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455203</v>
+        <v>455341</v>
       </c>
       <c r="R12" t="n">
-        <v>7037250</v>
+        <v>7037311</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,7 +2016,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2042,7 +2026,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,22 +2040,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På bark på stam av levande gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2089,7 +2073,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107085</v>
+        <v>121107087</v>
       </c>
       <c r="B13" t="n">
         <v>79143</v>
@@ -2124,7 +2108,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2138,10 +2122,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455213</v>
+        <v>455203</v>
       </c>
       <c r="R13" t="n">
-        <v>7037273</v>
+        <v>7037250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2173,7 +2157,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2183,7 +2167,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,7 +2181,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>I lövskog, med sälg, gråal</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2230,10 +2214,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107079</v>
+        <v>121107072</v>
       </c>
       <c r="B14" t="n">
-        <v>100364</v>
+        <v>74713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2242,25 +2226,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2270,10 +2254,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455347</v>
+        <v>455342</v>
       </c>
       <c r="R14" t="n">
-        <v>7037326</v>
+        <v>7037294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,7 +2289,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2315,7 +2299,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,7 +2313,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I västbrant med asprik granskog</t>
+          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2347,10 +2346,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107074</v>
+        <v>121107077</v>
       </c>
       <c r="B15" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2363,21 +2362,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2387,10 +2386,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455341</v>
+        <v>455339</v>
       </c>
       <c r="R15" t="n">
-        <v>7037311</v>
+        <v>7037327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2422,7 +2421,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2432,7 +2431,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,7 +2445,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I gammal granskog i västsluttning nedanför västbrant</t>
+          <t>I västbrant med asprik granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2461,7 +2460,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran # Picea abies</t>
+          <t>På äldre gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2479,10 +2478,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107086</v>
+        <v>121107083</v>
       </c>
       <c r="B16" t="n">
-        <v>79143</v>
+        <v>79592</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2491,47 +2490,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455210</v>
+        <v>455313</v>
       </c>
       <c r="R16" t="n">
-        <v>7037259</v>
+        <v>7037356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2563,7 +2553,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2573,7 +2563,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2587,22 +2577,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I sälgdominerande skog med inslag av contortatall</t>
+          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På sälg # Salix caprea</t>
+          <t>På bark på stam av levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2620,10 +2610,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107082</v>
+        <v>121107086</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>79143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2636,26 +2626,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1352</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2665,14 +2655,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kläppbergets västbrant, knappt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppbergets västbrant, drygt 1,5 km NO Änge, Offerdal, Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455314</v>
+        <v>455210</v>
       </c>
       <c r="R17" t="n">
-        <v>7037356</v>
+        <v>7037259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2704,7 +2694,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2714,7 +2704,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,12 +2718,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I västbrant med lövrik skog i branten och granskog nedanför</t>
+          <t>I sälgdominerande skog med inslag av contortatall</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På klippa</t>
+          <t>På sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
